--- a/grupos/5ALCV - Estadisticos 20231.xlsx
+++ b/grupos/5ALCV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="116">
   <si>
     <t>Materia</t>
   </si>
@@ -146,7 +146,7 @@
     <t>SANJUAN MARTINEZ ALMA KAREN</t>
   </si>
   <si>
-    <t>TENTZOHUA LEÓN RUBI</t>
+    <t>TENTZOHUA LEON RUBI</t>
   </si>
   <si>
     <t>VAZQUEZ VERA MARIA JOSE</t>
@@ -200,12 +200,12 @@
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,142 +224,148 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>QUIÑONES</t>
   </si>
   <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>ABIGAIL</t>
   </si>
   <si>
     <t>MIROSLAVA</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ITZEL ABIGAIL</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>CITLALI ESPERANZA</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
     <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>AMY JULIET</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
   </si>
 </sst>
 </file>
@@ -867,13 +873,13 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -882,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -944,13 +950,13 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -959,7 +965,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1021,13 +1027,13 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1036,7 +1042,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1098,13 +1104,13 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1113,7 +1119,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1175,13 +1181,13 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1190,7 +1196,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1211,13 +1217,13 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>7</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1226,7 +1232,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1252,13 +1258,13 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1267,7 +1273,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1288,13 +1294,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>10</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1303,7 +1309,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1329,13 +1335,13 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1344,7 +1350,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1365,13 +1371,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>7</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1380,7 +1386,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1406,13 +1412,13 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1421,7 +1427,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1442,13 +1448,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>8</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1457,7 +1463,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1483,13 +1489,13 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1498,7 +1504,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1534,7 +1540,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1560,13 +1566,13 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1575,7 +1581,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1596,13 +1602,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>8</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1611,7 +1617,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1637,13 +1643,13 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1652,7 +1658,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1688,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1714,13 +1720,13 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1729,7 +1735,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1756,7 +1762,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1791,13 +1797,13 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1806,7 +1812,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1827,7 +1833,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -1868,13 +1874,13 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1883,7 +1889,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1904,7 +1910,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -1919,7 +1925,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1945,13 +1951,13 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -1960,7 +1966,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1987,7 +1993,7 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2022,13 +2028,13 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2037,7 +2043,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2058,7 +2064,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>8</v>
@@ -2073,7 +2079,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2099,13 +2105,13 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2114,7 +2120,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2176,13 +2182,13 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2191,7 +2197,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2212,7 +2218,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2227,7 +2233,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2253,13 +2259,13 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2268,7 +2274,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2330,13 +2336,13 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2345,7 +2351,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2366,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2381,7 +2387,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2407,13 +2413,13 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2422,7 +2428,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2443,13 +2449,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>8</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2458,7 +2464,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2484,13 +2490,13 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2499,7 +2505,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2561,13 +2567,13 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2576,7 +2582,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2597,7 +2603,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -2612,7 +2618,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2638,13 +2644,13 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2653,7 +2659,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2680,7 +2686,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2715,13 +2721,13 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2730,7 +2736,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2751,13 +2757,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>8</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2766,7 +2772,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2792,13 +2798,13 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -2807,7 +2813,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2869,13 +2875,13 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -2884,7 +2890,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2905,7 +2911,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -2920,7 +2926,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2946,13 +2952,13 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -2961,7 +2967,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2982,7 +2988,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>7</v>
@@ -2997,7 +3003,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3023,13 +3029,13 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I32">
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3038,7 +3044,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3074,7 +3080,7 @@
         <v>5</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3100,13 +3106,13 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3115,7 +3121,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3136,7 +3142,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3151,7 +3157,7 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3177,13 +3183,13 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3192,7 +3198,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3213,7 +3219,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -3228,7 +3234,7 @@
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3254,13 +3260,13 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3269,7 +3275,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3290,7 +3296,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3305,7 +3311,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3331,13 +3337,13 @@
         <v>9</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3346,7 +3352,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3373,7 +3379,7 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>8</v>
@@ -4285,7 +4291,7 @@
         <v>86.7</v>
       </c>
       <c r="H17">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="I17">
         <v>85</v>
@@ -4300,10 +4306,10 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="N17">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O17">
         <v>85</v>
@@ -4318,7 +4324,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -5505,19 +5511,19 @@
         <v>33</v>
       </c>
       <c r="D2">
+        <v>17</v>
+      </c>
+      <c r="E2">
         <v>16</v>
       </c>
-      <c r="E2">
-        <v>17</v>
-      </c>
       <c r="F2" s="2">
+        <v>51.5</v>
+      </c>
+      <c r="G2" s="2">
         <v>48.5</v>
       </c>
-      <c r="G2" s="2">
-        <v>51.5</v>
-      </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5569,19 +5575,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>93.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="G4" s="2">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5592,7 +5598,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -5601,19 +5607,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5624,10 +5630,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6">
         <v>33</v>
@@ -5645,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5656,7 +5662,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -5677,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5765,10 +5771,10 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5788,10 +5794,10 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5811,10 +5817,10 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5834,10 +5840,10 @@
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5851,16 +5857,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920102</v>
+        <v>21330051920080</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5874,16 +5880,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920102</v>
+        <v>21330051920080</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5897,16 +5903,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920104</v>
+        <v>21330051920102</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5920,16 +5926,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920104</v>
+        <v>21330051920102</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5949,10 +5955,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5972,10 +5978,10 @@
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -5989,22 +5995,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920109</v>
+        <v>21330051920077</v>
       </c>
       <c r="B12" t="s">
         <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6012,22 +6018,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920109</v>
+        <v>21330051920260</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6035,16 +6041,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920077</v>
+        <v>21330051920082</v>
       </c>
       <c r="B14" t="s">
         <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -6058,16 +6064,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920300</v>
+        <v>21330051920305</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -6081,16 +6087,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920260</v>
+        <v>21330051920089</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -6104,22 +6110,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920082</v>
+        <v>21330051920092</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -6127,16 +6133,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920083</v>
+        <v>21330051920093</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -6150,16 +6156,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920089</v>
+        <v>21330051920097</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -6173,16 +6179,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920093</v>
+        <v>21330051920099</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -6196,16 +6202,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920097</v>
+        <v>21330051920100</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -6219,16 +6225,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920100</v>
+        <v>21330051920101</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -6242,16 +6248,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920101</v>
+        <v>21330051920103</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -6265,22 +6271,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920103</v>
+        <v>21330051920104</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G24">
         <v>5</v>

--- a/grupos/5ALCV - Estadisticos 20231.xlsx
+++ b/grupos/5ALCV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -197,12 +197,12 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
@@ -218,30 +218,24 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
@@ -266,36 +260,27 @@
     <t>SANJUAN</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>BRETON</t>
   </si>
   <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -314,33 +299,24 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>RUBI</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
     <t>MARIA TERESA</t>
   </si>
   <si>
     <t>VANESSA AMAIRANY</t>
   </si>
   <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
     <t>FATIMA MARILYN</t>
   </si>
   <si>
@@ -363,9 +339,6 @@
   </si>
   <si>
     <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
   </si>
 </sst>
 </file>
@@ -876,16 +849,16 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>8</v>
@@ -912,13 +885,13 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -953,16 +926,16 @@
         <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -989,13 +962,13 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1030,16 +1003,16 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -1066,16 +1039,16 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1107,16 +1080,16 @@
         <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -1143,13 +1116,13 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1184,16 +1157,16 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -1220,16 +1193,16 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1261,16 +1234,16 @@
         <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -1303,10 +1276,10 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1338,16 +1311,16 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>7</v>
@@ -1374,13 +1347,13 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1415,16 +1388,16 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1451,16 +1424,16 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>8</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1492,16 +1465,16 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1528,16 +1501,16 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>6</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1569,16 +1542,16 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -1611,7 +1584,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1646,16 +1619,16 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -1682,13 +1655,13 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>5</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1723,16 +1696,16 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>8</v>
@@ -1765,7 +1738,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1800,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1809,7 +1782,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -1836,7 +1809,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -1845,7 +1818,7 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1877,16 +1850,16 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -1922,7 +1895,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -1954,16 +1927,16 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -1990,13 +1963,13 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>6</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2031,16 +2004,16 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -2073,10 +2046,10 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2108,16 +2081,16 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>8</v>
@@ -2144,7 +2117,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2153,7 +2126,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2185,16 +2158,16 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -2221,16 +2194,16 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2262,16 +2235,16 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>8</v>
@@ -2298,16 +2271,16 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2339,16 +2312,16 @@
         <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -2375,16 +2348,16 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2416,16 +2389,16 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>8</v>
@@ -2458,7 +2431,7 @@
         <v>5</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2493,16 +2466,16 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -2529,7 +2502,7 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -2570,16 +2543,16 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -2606,16 +2579,16 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>5</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2647,16 +2620,16 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>8</v>
@@ -2683,7 +2656,7 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2724,16 +2697,16 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>8</v>
@@ -2801,7 +2774,7 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>6</v>
@@ -2810,7 +2783,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>7</v>
@@ -2837,7 +2810,7 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -2878,16 +2851,16 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>7</v>
@@ -2914,13 +2887,13 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>5</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -2955,16 +2928,16 @@
         <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>9</v>
@@ -2991,16 +2964,16 @@
         <v>9</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>9</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -3032,16 +3005,16 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>6</v>
@@ -3074,10 +3047,10 @@
         <v>5</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3109,16 +3082,16 @@
         <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>5</v>
@@ -3145,16 +3118,16 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>5</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3186,16 +3159,16 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>7</v>
@@ -3228,7 +3201,7 @@
         <v>5</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>5</v>
@@ -3263,7 +3236,7 @@
         <v>7</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>6</v>
@@ -3272,7 +3245,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>5</v>
@@ -3299,7 +3272,7 @@
         <v>7</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>5</v>
@@ -3340,16 +3313,16 @@
         <v>9</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
         <v>9</v>
@@ -3376,13 +3349,13 @@
         <v>9</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>7</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>9</v>
@@ -3527,16 +3500,16 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>65</v>
+        <v>82.5</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="M4">
         <v>100</v>
@@ -3545,16 +3518,16 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>65</v>
+        <v>82.5</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3645,7 +3618,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3654,7 +3627,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>80</v>
+        <v>77.8</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -3663,7 +3636,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3672,7 +3645,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>80</v>
+        <v>77.8</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -3704,16 +3677,16 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>65</v>
+        <v>72.5</v>
       </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>82.2</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -3722,16 +3695,16 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>65</v>
+        <v>72.5</v>
       </c>
       <c r="P7">
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>82.2</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3763,16 +3736,16 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -3781,16 +3754,16 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3822,13 +3795,13 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -3840,13 +3813,13 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P9">
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -3881,7 +3854,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3899,7 +3872,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3940,16 +3913,16 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L11">
-        <v>90</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -3958,16 +3931,16 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R11">
-        <v>90</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3999,13 +3972,13 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L12">
         <v>80</v>
@@ -4017,13 +3990,13 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="P12">
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R12">
         <v>80</v>
@@ -4067,7 +4040,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -4085,7 +4058,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4117,16 +4090,16 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L14">
-        <v>90</v>
+        <v>73.3</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -4135,16 +4108,16 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R14">
-        <v>90</v>
+        <v>73.3</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4176,13 +4149,13 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -4194,13 +4167,13 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -4235,16 +4208,16 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>95</v>
+        <v>47.5</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>82.2</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -4253,16 +4226,16 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>95</v>
+        <v>47.5</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>82.2</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4294,16 +4267,16 @@
         <v>93.3</v>
       </c>
       <c r="I17">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M17">
         <v>93.3</v>
@@ -4312,16 +4285,16 @@
         <v>93.3</v>
       </c>
       <c r="O17">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="S17">
         <v>93.3</v>
@@ -4353,14 +4326,14 @@
         <v>100</v>
       </c>
       <c r="I18">
+        <v>97.5</v>
+      </c>
+      <c r="J18">
+        <v>100</v>
+      </c>
+      <c r="K18">
         <v>95</v>
       </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
-      <c r="K18">
-        <v>90</v>
-      </c>
       <c r="L18">
         <v>100</v>
       </c>
@@ -4371,13 +4344,13 @@
         <v>100</v>
       </c>
       <c r="O18">
+        <v>97.5</v>
+      </c>
+      <c r="P18">
+        <v>100</v>
+      </c>
+      <c r="Q18">
         <v>95</v>
-      </c>
-      <c r="P18">
-        <v>100</v>
-      </c>
-      <c r="Q18">
-        <v>90</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4412,13 +4385,13 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -4430,13 +4403,13 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P19">
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4530,7 +4503,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -4548,7 +4521,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4589,7 +4562,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -4607,7 +4580,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4648,7 +4621,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4657,7 +4630,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -4666,7 +4639,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4675,7 +4648,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4707,7 +4680,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -4725,7 +4698,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -4766,7 +4739,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -4784,7 +4757,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4825,14 +4798,14 @@
         <v>100</v>
       </c>
       <c r="I26">
+        <v>87.5</v>
+      </c>
+      <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
         <v>95</v>
       </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
-      <c r="K26">
-        <v>90</v>
-      </c>
       <c r="L26">
         <v>100</v>
       </c>
@@ -4843,13 +4816,13 @@
         <v>100</v>
       </c>
       <c r="O26">
+        <v>87.5</v>
+      </c>
+      <c r="P26">
+        <v>100</v>
+      </c>
+      <c r="Q26">
         <v>95</v>
-      </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
-      <c r="Q26">
-        <v>90</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -4943,13 +4916,13 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -4961,13 +4934,13 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="P28">
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -5002,16 +4975,16 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -5020,16 +4993,16 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="P29">
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -5061,7 +5034,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5079,7 +5052,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -5120,7 +5093,7 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J31">
         <v>100</v>
@@ -5138,7 +5111,7 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -5179,16 +5152,16 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L32">
-        <v>85</v>
+        <v>93.3</v>
       </c>
       <c r="M32">
         <v>100</v>
@@ -5197,16 +5170,16 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="P32">
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R32">
-        <v>85</v>
+        <v>93.3</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -5238,7 +5211,7 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5256,7 +5229,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5297,13 +5270,13 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -5315,13 +5288,13 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="P34">
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -5356,34 +5329,34 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
+        <v>42.5</v>
+      </c>
+      <c r="L35">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="M35">
+        <v>100</v>
+      </c>
+      <c r="N35">
+        <v>100</v>
+      </c>
+      <c r="O35">
         <v>85</v>
       </c>
-      <c r="L35">
-        <v>80</v>
-      </c>
-      <c r="M35">
-        <v>100</v>
-      </c>
-      <c r="N35">
-        <v>100</v>
-      </c>
-      <c r="O35">
-        <v>90</v>
-      </c>
       <c r="P35">
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>85</v>
+        <v>42.5</v>
       </c>
       <c r="R35">
-        <v>80</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -5543,19 +5516,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>72.7</v>
+        <v>84.8</v>
       </c>
       <c r="G3" s="2">
-        <v>27.3</v>
+        <v>15.2</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5566,7 +5539,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -5575,19 +5548,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>97</v>
+        <v>84.8</v>
       </c>
       <c r="G4" s="2">
-        <v>3</v>
+        <v>15.2</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5598,7 +5571,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -5607,19 +5580,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5630,10 +5603,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6">
         <v>33</v>
@@ -5651,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5733,7 +5706,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5765,16 +5738,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>21330051920305</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5788,22 +5761,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920071</v>
+        <v>21330051920305</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5811,16 +5784,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920078</v>
+        <v>21330051920102</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5834,22 +5807,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920078</v>
+        <v>21330051920102</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5857,16 +5830,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920080</v>
+        <v>21330051920107</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5880,16 +5853,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920080</v>
+        <v>21330051920107</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5903,22 +5876,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920102</v>
+        <v>21330051920077</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5926,22 +5899,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920102</v>
+        <v>21330051920260</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5949,16 +5922,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920107</v>
+        <v>21330051920080</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5972,16 +5945,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920107</v>
+        <v>21330051920082</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -5995,22 +5968,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920077</v>
+        <v>21330051920089</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6018,16 +5991,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920260</v>
+        <v>21330051920092</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -6041,22 +6014,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920082</v>
+        <v>21330051920093</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6064,16 +6037,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920305</v>
+        <v>21330051920097</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -6087,16 +6060,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920089</v>
+        <v>21330051920099</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -6110,16 +6083,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920092</v>
+        <v>21330051920100</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -6133,16 +6106,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920093</v>
+        <v>21330051920101</v>
       </c>
       <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
         <v>76</v>
       </c>
-      <c r="C18" t="s">
-        <v>79</v>
-      </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -6156,16 +6129,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920097</v>
+        <v>21330051920103</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -6174,121 +6147,6 @@
         <v>57</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920099</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920100</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920101</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920103</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920104</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20231.xlsx
+++ b/grupos/5ALCV - Estadisticos 20231.xlsx
@@ -194,10 +194,10 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
     <t>Flores Ovalle Victor</t>
@@ -1779,7 +1779,7 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -1815,7 +1815,7 @@
         <v>5</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -2780,7 +2780,7 @@
         <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>9</v>
@@ -2816,7 +2816,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3242,7 +3242,7 @@
         <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -3278,7 +3278,7 @@
         <v>5</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X35">
         <v>5</v>
@@ -4214,7 +4214,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>47.5</v>
+        <v>87.5</v>
       </c>
       <c r="L16">
         <v>82.2</v>
@@ -4232,7 +4232,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>47.5</v>
+        <v>87.5</v>
       </c>
       <c r="R16">
         <v>82.2</v>
@@ -4981,7 +4981,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L29">
         <v>95.59999999999999</v>
@@ -4999,7 +4999,7 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="R29">
         <v>95.59999999999999</v>
@@ -5335,7 +5335,7 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>42.5</v>
+        <v>82.5</v>
       </c>
       <c r="L35">
         <v>68.90000000000001</v>
@@ -5353,7 +5353,7 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>42.5</v>
+        <v>82.5</v>
       </c>
       <c r="R35">
         <v>68.90000000000001</v>
@@ -5507,7 +5507,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -5516,19 +5516,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>84.8</v>
+        <v>81.8</v>
       </c>
       <c r="G3" s="2">
-        <v>15.2</v>
+        <v>18.2</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -5560,7 +5560,7 @@
         <v>15.2</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>33</v>
@@ -5776,7 +5776,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5822,7 +5822,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5868,7 +5868,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5891,7 +5891,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5960,7 +5960,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>

--- a/grupos/5ALCV - Estadisticos 20231.xlsx
+++ b/grupos/5ALCV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -191,12 +191,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -218,46 +218,49 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>JUSTO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>NEGRETE</t>
@@ -266,79 +269,28 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
   </si>
   <si>
     <t>MARIA MICHELLE</t>
   </si>
   <si>
     <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
   </si>
 </sst>
 </file>
@@ -864,28 +816,28 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -894,10 +846,10 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -941,25 +893,25 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -974,7 +926,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1018,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1051,7 +1003,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1095,22 +1047,22 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1119,7 +1071,7 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1172,31 +1124,31 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>9</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1205,7 +1157,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1249,25 +1201,25 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1282,7 +1234,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1326,31 +1278,31 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>8</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1403,22 +1355,22 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1427,13 +1379,13 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>7</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1480,28 +1432,28 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>7</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1557,28 +1509,28 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>8</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1587,7 +1539,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1634,22 +1586,22 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1711,31 +1663,31 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1744,7 +1696,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1788,22 +1740,22 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>6</v>
@@ -1812,13 +1764,13 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1865,22 +1817,22 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>6</v>
@@ -1895,7 +1847,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -1942,22 +1894,22 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -1966,7 +1918,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2019,22 +1971,22 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2043,7 +1995,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2096,28 +2048,28 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>9</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2129,7 +2081,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2173,31 +2125,31 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>6</v>
@@ -2206,7 +2158,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2250,22 +2202,22 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2327,31 +2279,31 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>9</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2360,7 +2312,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2404,22 +2356,22 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2428,13 +2380,13 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>6</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2481,22 +2433,22 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2505,7 +2457,7 @@
         <v>9</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2514,7 +2466,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2558,31 +2510,31 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>8</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2591,7 +2543,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2635,22 +2587,22 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2712,31 +2664,31 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2745,7 +2697,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2789,31 +2741,31 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -2822,7 +2774,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2866,31 +2818,31 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>8</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -2943,31 +2895,31 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>9</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -2976,7 +2928,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3020,31 +2972,31 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>5</v>
@@ -3097,22 +3049,22 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>7</v>
@@ -3121,7 +3073,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>6</v>
@@ -3174,40 +3126,40 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
         <v>7</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>6</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3251,31 +3203,31 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>7</v>
       </c>
       <c r="V35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>5</v>
@@ -3284,7 +3236,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3328,22 +3280,22 @@
         <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3527,7 +3479,7 @@
         <v>82.5</v>
       </c>
       <c r="R4">
-        <v>91.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3577,7 +3529,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3636,7 +3588,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3645,7 +3597,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>77.8</v>
+        <v>86.7</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -3695,7 +3647,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>72.5</v>
+        <v>45.3</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3704,10 +3656,10 @@
         <v>92.5</v>
       </c>
       <c r="R7">
-        <v>82.2</v>
+        <v>89.3</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3754,7 +3706,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -3763,7 +3715,7 @@
         <v>92.5</v>
       </c>
       <c r="R8">
-        <v>93.3</v>
+        <v>96</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3813,7 +3765,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3872,7 +3824,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3931,7 +3883,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>87.5</v>
+        <v>54.7</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3940,7 +3892,7 @@
         <v>97.5</v>
       </c>
       <c r="R11">
-        <v>95.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3990,7 +3942,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>82.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -3999,7 +3951,7 @@
         <v>95</v>
       </c>
       <c r="R12">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4049,7 +4001,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4058,7 +4010,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>95.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4108,7 +4060,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>87.5</v>
+        <v>54.7</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4117,7 +4069,7 @@
         <v>97.5</v>
       </c>
       <c r="R14">
-        <v>73.3</v>
+        <v>50.7</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4167,7 +4119,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>92.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4226,7 +4178,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>87.5</v>
+        <v>54.7</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4235,7 +4187,7 @@
         <v>87.5</v>
       </c>
       <c r="R16">
-        <v>82.2</v>
+        <v>69.3</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4282,10 +4234,10 @@
         <v>93.3</v>
       </c>
       <c r="N17">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="O17">
-        <v>82.5</v>
+        <v>81.3</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4294,10 +4246,10 @@
         <v>87.5</v>
       </c>
       <c r="R17">
-        <v>93.3</v>
+        <v>96</v>
       </c>
       <c r="S17">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4344,7 +4296,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -4403,7 +4355,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -4462,7 +4414,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4521,7 +4473,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4580,7 +4532,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4639,7 +4591,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4648,7 +4600,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>95.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4698,7 +4650,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -4757,7 +4709,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4816,7 +4768,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -5002,7 +4954,7 @@
         <v>90</v>
       </c>
       <c r="R29">
-        <v>95.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -5052,7 +5004,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -5111,7 +5063,7 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -5170,7 +5122,7 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>82.5</v>
+        <v>81.3</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -5179,7 +5131,7 @@
         <v>97.5</v>
       </c>
       <c r="R32">
-        <v>93.3</v>
+        <v>96</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -5229,7 +5181,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>85</v>
+        <v>53.1</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5288,7 +5240,7 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>82.5</v>
+        <v>81.3</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5347,7 +5299,7 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>85</v>
+        <v>53.1</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -5356,7 +5308,7 @@
         <v>82.5</v>
       </c>
       <c r="R35">
-        <v>68.90000000000001</v>
+        <v>48</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -5475,7 +5427,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -5484,19 +5436,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>51.5</v>
+        <v>81.8</v>
       </c>
       <c r="G2" s="2">
-        <v>48.5</v>
+        <v>18.2</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5507,7 +5459,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -5516,16 +5468,16 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>81.8</v>
+        <v>84.8</v>
       </c>
       <c r="G3" s="2">
-        <v>18.2</v>
+        <v>15.2</v>
       </c>
       <c r="H3">
         <v>6.5</v>
@@ -5548,19 +5500,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>15.2</v>
+        <v>12.1</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5571,28 +5523,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>33</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5603,10 +5555,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6">
         <v>33</v>
@@ -5624,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5656,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5706,7 +5658,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5738,22 +5690,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920305</v>
+        <v>21330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5761,22 +5713,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920305</v>
+        <v>21330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5784,22 +5736,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920102</v>
+        <v>21330051920082</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5807,22 +5759,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920102</v>
+        <v>21330051920082</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5830,19 +5782,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920107</v>
+        <v>21330051920109</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>57</v>
@@ -5853,16 +5805,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920107</v>
+        <v>21330051920109</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5876,19 +5828,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920077</v>
+        <v>21330051920075</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>58</v>
@@ -5899,19 +5851,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920260</v>
+        <v>21330051920077</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>57</v>
@@ -5922,22 +5874,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920080</v>
+        <v>21330051920260</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5945,22 +5897,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920082</v>
+        <v>21330051920080</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5968,19 +5920,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920089</v>
+        <v>21330051920305</v>
       </c>
       <c r="B12" t="s">
         <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
         <v>57</v>
@@ -5991,162 +5943,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920092</v>
+        <v>21330051920102</v>
       </c>
       <c r="B13" t="s">
         <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
         <v>57</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920093</v>
-      </c>
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920097</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920099</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920100</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920101</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920103</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20231.xlsx
+++ b/grupos/5ALCV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -191,15 +191,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
@@ -218,79 +218,55 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>BRETON</t>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>MIROSLAVA</t>
   </si>
   <si>
     <t>ABIGAIL</t>
   </si>
   <si>
-    <t>VANESSA AMAIRANY</t>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
   </si>
 </sst>
 </file>
@@ -825,7 +801,7 @@
         <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>9</v>
@@ -843,7 +819,7 @@
         <v>5</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -902,7 +878,7 @@
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -920,7 +896,7 @@
         <v>6</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -979,7 +955,7 @@
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>7</v>
@@ -997,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1056,7 +1032,7 @@
         <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>5</v>
@@ -1074,7 +1050,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1133,7 +1109,7 @@
         <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -1151,7 +1127,7 @@
         <v>7</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1210,7 +1186,7 @@
         <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -1287,7 +1263,7 @@
         <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -1364,7 +1340,7 @@
         <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>5</v>
@@ -1382,7 +1358,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1441,7 +1417,7 @@
         <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>7</v>
@@ -1459,7 +1435,7 @@
         <v>6</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1518,7 +1494,7 @@
         <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -1536,7 +1512,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1595,7 +1571,7 @@
         <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>5</v>
@@ -1613,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1672,7 +1648,7 @@
         <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>10</v>
@@ -1749,7 +1725,7 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>5</v>
@@ -1826,7 +1802,7 @@
         <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>10</v>
@@ -1903,7 +1879,7 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -1980,7 +1956,7 @@
         <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>10</v>
@@ -1998,7 +1974,7 @@
         <v>6</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2057,7 +2033,7 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -2134,7 +2110,7 @@
         <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>10</v>
@@ -2211,7 +2187,7 @@
         <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -2288,7 +2264,7 @@
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>10</v>
@@ -2365,7 +2341,7 @@
         <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>6</v>
@@ -2383,7 +2359,7 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>6</v>
@@ -2442,7 +2418,7 @@
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -2519,7 +2495,7 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
         <v>10</v>
@@ -2596,7 +2572,7 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -2614,7 +2590,7 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2673,7 +2649,7 @@
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>7</v>
@@ -2750,7 +2726,7 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>9</v>
@@ -2827,7 +2803,7 @@
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -2845,7 +2821,7 @@
         <v>6</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -2904,7 +2880,7 @@
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -2922,7 +2898,7 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -2981,7 +2957,7 @@
         <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
         <v>7</v>
@@ -2999,7 +2975,7 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -3058,7 +3034,7 @@
         <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
         <v>8</v>
@@ -3135,7 +3111,7 @@
         <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>8</v>
@@ -3212,7 +3188,7 @@
         <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
         <v>5</v>
@@ -3230,7 +3206,7 @@
         <v>6</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>5</v>
@@ -3289,7 +3265,7 @@
         <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>10</v>
@@ -3476,7 +3452,7 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R4">
         <v>94.7</v>
@@ -3535,7 +3511,7 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -3594,7 +3570,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R6">
         <v>86.7</v>
@@ -3653,7 +3629,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>92.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="R7">
         <v>89.3</v>
@@ -3712,7 +3688,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="R8">
         <v>96</v>
@@ -3771,7 +3747,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -3830,7 +3806,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -3889,7 +3865,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="R11">
         <v>97.3</v>
@@ -3948,7 +3924,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="R12">
         <v>88</v>
@@ -4066,7 +4042,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="R14">
         <v>50.7</v>
@@ -4125,7 +4101,7 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -4184,7 +4160,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R16">
         <v>69.3</v>
@@ -4243,7 +4219,7 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R17">
         <v>96</v>
@@ -4302,7 +4278,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4361,7 +4337,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4420,7 +4396,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -4656,7 +4632,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4715,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -4774,7 +4750,7 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -4892,7 +4868,7 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -4951,7 +4927,7 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="R29">
         <v>97.3</v>
@@ -5010,7 +4986,7 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -5128,7 +5104,7 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="R32">
         <v>96</v>
@@ -5187,7 +5163,7 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -5246,7 +5222,7 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -5305,7 +5281,7 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
       <c r="R35">
         <v>48</v>
@@ -5427,7 +5403,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -5436,16 +5412,16 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>81.8</v>
+        <v>84.8</v>
       </c>
       <c r="G2" s="2">
-        <v>18.2</v>
+        <v>15.2</v>
       </c>
       <c r="H2">
         <v>6.5</v>
@@ -5459,7 +5435,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -5468,19 +5444,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>15.2</v>
+        <v>12.1</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5491,7 +5467,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -5500,19 +5476,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>87.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="G4" s="2">
-        <v>12.1</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5526,7 +5502,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>33</v>
@@ -5658,7 +5634,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5690,22 +5666,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>21330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5713,22 +5689,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920071</v>
+        <v>21330051920078</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5736,22 +5712,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920082</v>
+        <v>21330051920071</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5759,22 +5735,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920082</v>
+        <v>21330051920075</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5782,22 +5758,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920109</v>
+        <v>21330051920260</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5805,22 +5781,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920109</v>
+        <v>21330051920080</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5828,139 +5804,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920075</v>
+        <v>21330051920109</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>58</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920077</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920260</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920080</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920305</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920102</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20231.xlsx
+++ b/grupos/5ALCV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -191,15 +191,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
@@ -218,55 +218,70 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>ESPIRITU</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>VERA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>ABIGAIL</t>
   </si>
   <si>
+    <t>REYLI</t>
+  </si>
+  <si>
     <t>EVELYN JOHANA</t>
   </si>
   <si>
-    <t>MARIA TERESA</t>
+    <t>YARED</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
-    <t>MARIA JOSE</t>
+    <t>ALMA KAREN</t>
   </si>
 </sst>
 </file>
@@ -949,7 +964,7 @@
         <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P6">
         <v>10</v>
@@ -967,7 +982,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1026,7 +1041,7 @@
         <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>5</v>
@@ -1044,7 +1059,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1334,7 +1349,7 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P11">
         <v>5</v>
@@ -1352,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1565,7 +1580,7 @@
         <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>5</v>
@@ -1583,7 +1598,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1719,7 +1734,7 @@
         <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P16">
         <v>8</v>
@@ -1737,7 +1752,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -3028,7 +3043,7 @@
         <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P33">
         <v>7</v>
@@ -3046,7 +3061,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>6</v>
@@ -3182,7 +3197,7 @@
         <v>6</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P35">
         <v>7</v>
@@ -3200,7 +3215,7 @@
         <v>6</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V35">
         <v>6</v>
@@ -3564,7 +3579,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>56.3</v>
+        <v>79.7</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3623,7 +3638,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>45.3</v>
+        <v>48.4</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3859,7 +3874,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>54.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -4036,7 +4051,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>54.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4154,7 +4169,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>54.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -5157,7 +5172,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>53.1</v>
+        <v>75</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5403,7 +5418,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -5412,19 +5427,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>84.8</v>
+        <v>78.8</v>
       </c>
       <c r="G2" s="2">
-        <v>15.2</v>
+        <v>21.2</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5435,7 +5450,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -5444,19 +5459,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>87.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="G3" s="2">
-        <v>12.1</v>
+        <v>15.2</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5467,7 +5482,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -5476,19 +5491,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>97</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>3</v>
+        <v>12.1</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5499,28 +5514,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5634,7 +5649,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5666,19 +5681,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920078</v>
+        <v>21330051920260</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>57</v>
@@ -5689,22 +5704,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920078</v>
+        <v>21330051920260</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5712,19 +5727,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920071</v>
+        <v>21330051920109</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>57</v>
@@ -5735,22 +5750,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920075</v>
+        <v>21330051920109</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5758,19 +5773,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920260</v>
+        <v>21330051920071</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>58</v>
@@ -5781,19 +5796,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920080</v>
+        <v>20330051920378</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
         <v>57</v>
@@ -5804,24 +5819,93 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920109</v>
+        <v>21330051920075</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>58</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920076</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920080</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920103</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20231.xlsx
+++ b/grupos/5ALCV - Estadisticos 20231.xlsx
@@ -825,22 +825,22 @@
         <v>8</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -902,22 +902,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -979,22 +979,22 @@
         <v>7</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>5</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1056,7 +1056,7 @@
         <v>6</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1071,7 +1071,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1133,22 +1133,22 @@
         <v>6</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1210,22 +1210,22 @@
         <v>8</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>10</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1287,22 +1287,22 @@
         <v>7</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1364,22 +1364,22 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>5</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1441,22 +1441,22 @@
         <v>6</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1518,22 +1518,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1595,7 +1595,7 @@
         <v>7</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -1604,13 +1604,13 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1672,22 +1672,22 @@
         <v>8</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1749,22 +1749,22 @@
         <v>7</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>5</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1826,22 +1826,22 @@
         <v>7</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>5</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1903,22 +1903,22 @@
         <v>8</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1980,22 +1980,22 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2057,22 +2057,22 @@
         <v>8</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2134,22 +2134,22 @@
         <v>7</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2211,22 +2211,22 @@
         <v>7</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2288,22 +2288,22 @@
         <v>8</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2365,22 +2365,22 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2442,22 +2442,22 @@
         <v>8</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2519,22 +2519,22 @@
         <v>7</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2596,22 +2596,22 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>10</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2673,22 +2673,22 @@
         <v>7</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2750,22 +2750,22 @@
         <v>6</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2827,22 +2827,22 @@
         <v>8</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2904,22 +2904,22 @@
         <v>8</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2981,22 +2981,22 @@
         <v>6</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3058,22 +3058,22 @@
         <v>8</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>5</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3135,22 +3135,22 @@
         <v>6</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3212,22 +3212,22 @@
         <v>7</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>5</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X35">
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3289,22 +3289,22 @@
         <v>8</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5439,7 +5439,7 @@
         <v>21.2</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5471,7 +5471,7 @@
         <v>15.2</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5503,7 +5503,7 @@
         <v>12.1</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5535,7 +5535,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5567,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5599,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5ALCV - Estadisticos 20231.xlsx
+++ b/grupos/5ALCV - Estadisticos 20231.xlsx
@@ -825,22 +825,22 @@
         <v>8</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -902,22 +902,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -979,22 +979,22 @@
         <v>7</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>5</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1056,7 +1056,7 @@
         <v>6</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1071,7 +1071,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1133,22 +1133,22 @@
         <v>6</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1210,22 +1210,22 @@
         <v>8</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>10</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1287,22 +1287,22 @@
         <v>7</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1364,22 +1364,22 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>5</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1441,22 +1441,22 @@
         <v>6</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1518,22 +1518,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1595,7 +1595,7 @@
         <v>7</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -1604,13 +1604,13 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1672,22 +1672,22 @@
         <v>8</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1749,22 +1749,22 @@
         <v>7</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>5</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1826,22 +1826,22 @@
         <v>7</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>5</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1903,22 +1903,22 @@
         <v>8</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1980,22 +1980,22 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2057,22 +2057,22 @@
         <v>8</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2134,22 +2134,22 @@
         <v>7</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2211,22 +2211,22 @@
         <v>7</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2288,22 +2288,22 @@
         <v>8</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2365,22 +2365,22 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2442,22 +2442,22 @@
         <v>8</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2519,22 +2519,22 @@
         <v>7</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2596,22 +2596,22 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>10</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2673,22 +2673,22 @@
         <v>7</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2750,22 +2750,22 @@
         <v>6</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2827,22 +2827,22 @@
         <v>8</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2904,22 +2904,22 @@
         <v>8</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2981,22 +2981,22 @@
         <v>6</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3058,22 +3058,22 @@
         <v>8</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>5</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3135,22 +3135,22 @@
         <v>6</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3212,22 +3212,22 @@
         <v>7</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>5</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3289,22 +3289,22 @@
         <v>8</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5439,7 +5439,7 @@
         <v>21.2</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5471,7 +5471,7 @@
         <v>15.2</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5503,7 +5503,7 @@
         <v>12.1</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5535,7 +5535,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5567,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5599,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
